--- a/src/test/resources/TEST_DATA/ObtainLoanData.xlsx
+++ b/src/test/resources/TEST_DATA/ObtainLoanData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>accountNumber1</t>
   </si>
@@ -42,13 +42,16 @@
     <t>accountNumber2</t>
   </si>
   <si>
-    <t>216758079687</t>
+    <t>successMsg</t>
+  </si>
+  <si>
+    <t>217557792199</t>
   </si>
   <si>
     <t>500</t>
   </si>
   <si>
-    <t>500000</t>
+    <t>500001</t>
   </si>
   <si>
     <t>10000</t>
@@ -63,7 +66,10 @@
     <t xml:space="preserve">Testing the obtain loan</t>
   </si>
   <si>
-    <t xml:space="preserve">0167 5100 0165</t>
+    <t xml:space="preserve">1019 5784 0910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Creation Successful</t>
   </si>
 </sst>
 </file>
@@ -98,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
@@ -107,6 +113,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,9 +622,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="6" style="1" width="9.140625"/>
+    <col customWidth="1" min="1" max="1" style="1" width="15.28125"/>
+    <col min="2" max="6" style="1" width="9.140625"/>
     <col customWidth="1" min="7" max="7" style="1" width="38.421875"/>
-    <col min="8" max="16384" style="1" width="9.140625"/>
+    <col customWidth="1" min="8" max="8" style="1" width="22.7109375"/>
+    <col customWidth="1" min="9" max="9" style="1" width="31.7109375"/>
+    <col min="10" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,31 +655,37 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
